--- a/InputData/ccs/CCP/CO2 Capture Potentials.xlsx
+++ b/InputData/ccs/CCP/CO2 Capture Potentials.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\ccs\CCP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\next\Dropbox\NEXT Group\20. 프로젝트 관리\2025 에너지 수요전망 모형 구축\EPS 모형\eps-southkorea-3.3.1\InputData\ccs\CCP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28C2AF75-4449-4234-82F2-ED89CB505329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADE422F0-36DF-4A53-A507-75F7AE1D9DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-14505" yWindow="1080" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -128,7 +128,7 @@
         <u/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -139,7 +139,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -158,7 +158,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -168,7 +168,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -184,7 +184,7 @@
         <b/>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -194,7 +194,7 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Calibri"/>
+        <rFont val="맑은 고딕"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
@@ -316,10 +316,10 @@
     <t>hydrogen combined cycle</t>
   </si>
   <si>
+    <t>capture rate</t>
+  </si>
+  <si>
     <t>natural gas reforming with CCS</t>
-  </si>
-  <si>
-    <t>capture rate</t>
   </si>
 </sst>
 </file>
@@ -327,13 +327,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -341,7 +341,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -349,7 +349,7 @@
       <i/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -358,14 +358,21 @@
       <u/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -400,16 +407,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -717,25 +724,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="103.42578125" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="22.140625" customWidth="1"/>
-    <col min="5" max="5" width="18.42578125" customWidth="1"/>
+    <col min="2" max="2" width="103.4140625" customWidth="1"/>
+    <col min="3" max="3" width="17.1640625" customWidth="1"/>
+    <col min="4" max="4" width="22.1640625" customWidth="1"/>
+    <col min="5" max="5" width="18.4140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -743,97 +750,98 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="B15" s="1"/>
       <c r="C15" s="2"/>
       <c r="D15" s="3"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>22</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>23</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>24</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>60</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="B21" s="1"/>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B22" s="6"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" s="5" t="s">
         <v>29</v>
       </c>
       <c r="B23" s="6"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>31</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
@@ -845,17 +853,17 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="30.140625" customWidth="1"/>
+    <col min="1" max="1" width="30.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -863,7 +871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>61</v>
       </c>
@@ -871,7 +879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>62</v>
       </c>
@@ -879,7 +887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -887,7 +895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -895,7 +903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -903,7 +911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -911,7 +919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -919,7 +927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -927,7 +935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -935,7 +943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -943,7 +951,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -951,7 +959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -959,7 +967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -967,7 +975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -975,7 +983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -983,7 +991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -991,7 +999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>63</v>
       </c>
@@ -999,7 +1007,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>64</v>
       </c>
@@ -1007,7 +1015,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>65</v>
       </c>
@@ -1015,7 +1023,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>66</v>
       </c>
@@ -1023,7 +1031,7 @@
         <v>0.95</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>67</v>
       </c>
@@ -1031,7 +1039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A24" s="7" t="s">
         <v>68</v>
       </c>
@@ -1039,7 +1047,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A25" s="7" t="s">
         <v>69</v>
       </c>
@@ -1048,6 +1056,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1059,14 +1068,14 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="45.42578125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+    <col min="1" max="1" width="45.4140625" customWidth="1"/>
+    <col min="2" max="2" width="24.75" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
         <v>20</v>
       </c>
@@ -1077,7 +1086,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -1088,7 +1097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -1099,7 +1108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>36</v>
       </c>
@@ -1110,7 +1119,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>37</v>
       </c>
@@ -1121,7 +1130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>38</v>
       </c>
@@ -1132,7 +1141,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>39</v>
       </c>
@@ -1143,7 +1152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>40</v>
       </c>
@@ -1154,7 +1163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>41</v>
       </c>
@@ -1165,7 +1174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>42</v>
       </c>
@@ -1176,7 +1185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>43</v>
       </c>
@@ -1187,7 +1196,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -1198,7 +1207,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>45</v>
       </c>
@@ -1209,7 +1218,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>46</v>
       </c>
@@ -1220,7 +1229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>47</v>
       </c>
@@ -1231,7 +1240,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>48</v>
       </c>
@@ -1242,7 +1251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A17" t="s">
         <v>49</v>
       </c>
@@ -1253,7 +1262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A18" t="s">
         <v>50</v>
       </c>
@@ -1264,7 +1273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A19" t="s">
         <v>51</v>
       </c>
@@ -1275,7 +1284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
         <v>52</v>
       </c>
@@ -1286,7 +1295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
         <v>53</v>
       </c>
@@ -1297,7 +1306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A22" t="s">
         <v>54</v>
       </c>
@@ -1308,7 +1317,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
         <v>55</v>
       </c>
@@ -1319,7 +1328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
         <v>56</v>
       </c>
@@ -1330,7 +1339,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
         <v>57</v>
       </c>
@@ -1341,7 +1350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
         <v>58</v>
       </c>
@@ -1353,40 +1362,213 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3D48B9D0-7C8A-4023-B3D1-3CE3C9AF0583}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC3D1964-2BAF-4F97-932D-12C1228476DE}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="45.42578125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="25.85546875" customWidth="1"/>
+    <col min="1" max="1" width="45.4140625" customWidth="1"/>
+    <col min="2" max="2" width="24.75" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
         <v>20</v>
       </c>
       <c r="B1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
         <v>71</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>70</v>
       </c>
       <c r="B2">
         <v>0.85</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E59C87379D9A4242BB3A95F198D6F941" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="07a235b40ffe2d9a960bde50f6511605">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="40f4d404-d193-41dc-bb72-733c1e774208" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="485fc8e6f691b86ce0aee9b7e82feca0" ns2:_="">
+    <xsd:import namespace="40f4d404-d193-41dc-bb72-733c1e774208"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="40f4d404-d193-41dc-bb72-733c1e774208" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{897E6505-A15D-4978-A5B0-A5D4F70F0821}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{47E4136B-3AB9-4A20-8DAE-0E6C65111D67}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{40F86BDE-0336-47E6-9BF8-1BAD7EE28B99}"/>
 </file>